--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-06</t>
+          <t>Ventas 2025-09-01 / 2025-09-13</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>35215.96</v>
+        <v>72110.14</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4203</v>
+        <v>8893</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>14084.01</v>
+        <v>29521.33</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1885</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6847.08</v>
+        <v>15263.98</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>910</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>20194.83</v>
+        <v>42334.37</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2575</v>
+        <v>5478</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>7141.78</v>
+        <v>15256.19</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>936</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>23551.29</v>
+        <v>53299.57</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2573</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>25287.09</v>
+        <v>53116.25</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3091</v>
+        <v>6626</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-13</t>
+          <t>Ventas 2025-09-01 / 2025-09-20</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>72110.14</v>
+        <v>111209.46</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>8893</v>
+        <v>13868</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>29521.33</v>
+        <v>46165.25</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3966</v>
+        <v>6229</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>15263.98</v>
+        <v>24289.61</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>2077</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>42334.37</v>
+        <v>64043.8</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>5478</v>
+        <v>8365</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>15256.19</v>
+        <v>21993.29</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2048</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>53299.57</v>
+        <v>84086.21000000001</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>5931</v>
+        <v>9373</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>53116.25</v>
+        <v>80435.10000000001</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>6626</v>
+        <v>10110</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-20</t>
+          <t>Ventas 2025-09-01 / 2025-09-27</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>111209.46</v>
+        <v>147898.63</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>13868</v>
+        <v>18456</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>46165.25</v>
+        <v>62769.88</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6229</v>
+        <v>8488</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>24289.61</v>
+        <v>32624.21</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>3352</v>
+        <v>4432</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>64043.8</v>
+        <v>85054.98</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>8365</v>
+        <v>11126</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>21993.29</v>
+        <v>28210.25</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2932</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>84086.21000000001</v>
+        <v>113258.2</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>9373</v>
+        <v>12691</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>80435.10000000001</v>
+        <v>107350.73</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>10110</v>
+        <v>13571</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-01 / 2025-09-27</t>
+          <t>Ventas 2025-10-01 / 2025-10-04</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>147898.63</v>
+        <v>23426.49</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>18456</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>62769.88</v>
+        <v>9009.27</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>8488</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>32624.21</v>
+        <v>4338.78</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>4432</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>85054.98</v>
+        <v>11226.41</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>11126</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>28210.25</v>
+        <v>3721.06</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>3777</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>113258.2</v>
+        <v>17353.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>12691</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>107350.73</v>
+        <v>16883.55</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>13571</v>
+        <v>2202</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-04</t>
+          <t>Ventas 2025-10-01 / 2025-10-11</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>23426.49</v>
+        <v>58789.03</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>2874</v>
+        <v>7263</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>9009.27</v>
+        <v>24038.07</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1275</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>4338.78</v>
+        <v>11034.96</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>618</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>11226.41</v>
+        <v>29740.59</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1525</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>3721.06</v>
+        <v>9315.99</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>17353.82</v>
+        <v>50234.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>1909</v>
+        <v>5487</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>16883.55</v>
+        <v>40086.49</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2202</v>
+        <v>5172</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-11</t>
+          <t>Ventas 2025-10-01 / 2025-10-18</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>58789.03</v>
+        <v>92090.94</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>7263</v>
+        <v>11447</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>24038.07</v>
+        <v>38249.87</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>3420</v>
+        <v>5394</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>11034.96</v>
+        <v>19197.42</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1547</v>
+        <v>2657</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>29740.59</v>
+        <v>48711.27</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>4022</v>
+        <v>6506</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>9315.99</v>
+        <v>15769.68</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1260</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>50234.18</v>
+        <v>80605.09</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>5487</v>
+        <v>8779</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>40086.49</v>
+        <v>64523.04</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>5172</v>
+        <v>8190</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_mensual_ant.xlsx
+++ b/Acumulado_mensual_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-01 / 2025-10-18</t>
+          <t>Ventas 2025-10-01 / 2025-10-25</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>92090.94</v>
+        <v>128924.7</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>11447</v>
+        <v>15966</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>38249.87</v>
+        <v>55813.53</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>5394</v>
+        <v>7790</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>19197.42</v>
+        <v>26714.42</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>2657</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>48711.27</v>
+        <v>69043.17999999999</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>6506</v>
+        <v>9137</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>15769.68</v>
+        <v>21668.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2146</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>80605.09</v>
+        <v>111873.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>8779</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>64523.04</v>
+        <v>92215.28999999999</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>8190</v>
+        <v>11605</v>
       </c>
     </row>
   </sheetData>
